--- a/outputs/evidences_Tests.xlsx
+++ b/outputs/evidences_Tests.xlsx
@@ -113,13 +113,13 @@
     <t xml:space="preserve">Eastern Europe</t>
   </si>
   <si>
-    <t xml:space="preserve">Northern Asia</t>
-  </si>
-  <si>
     <t xml:space="preserve">No clear association</t>
   </si>
   <si>
     <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern Asia</t>
   </si>
   <si>
     <t xml:space="preserve">Western Europe</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">Chi-square</t>
   </si>
   <si>
-    <t xml:space="preserve">Cramer's V = 0.130</t>
+    <t xml:space="preserve">Cramer's V = 0.128</t>
   </si>
   <si>
     <t xml:space="preserve">Positive (more than expected; peak in Central America for 'Medium')</t>
   </si>
   <si>
-    <t xml:space="preserve">Cramer's V = 0.179</t>
+    <t xml:space="preserve">Cramer's V = 0.181</t>
   </si>
   <si>
     <t xml:space="preserve">n_groups</t>
@@ -572,7 +572,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000000000000575873781739593</v>
+        <v>0.00000000000190782674949452</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -589,7 +589,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000000000000117705545509058</v>
+        <v>0.000000000000113581756001684</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -606,7 +606,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>0.833939336251376</v>
+        <v>0.835694191399225</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -623,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00438925594441673</v>
+        <v>0.00535558280746744</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -640,7 +640,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0000356995824438056</v>
+        <v>0.0000278845963036329</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -657,7 +657,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>0.184894071948028</v>
+        <v>0.191762733294381</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -674,7 +674,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>0.606595143808478</v>
+        <v>0.599818307459414</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -691,7 +691,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00000533440037065668</v>
+        <v>0.0000071069570614956</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -708,7 +708,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>0.33354297598723</v>
+        <v>0.298227376458743</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -725,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000649350114452409</v>
+        <v>0.000760548135174582</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -742,7 +742,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>0.43327099753918</v>
+        <v>0.386747821645991</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -759,7 +759,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00213952883542999</v>
+        <v>0.00310738343287872</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -776,7 +776,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00000000427821411347739</v>
+        <v>0.00000000348987851384652</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
@@ -793,7 +793,7 @@
         <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0777520115329659</v>
+        <v>0.0782543241952212</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -810,7 +810,7 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>0.826325520328091</v>
+        <v>0.825521628146571</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -827,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0774068754546591</v>
+        <v>0.0848640769248164</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -844,7 +844,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00105922354721658</v>
+        <v>0.000405626794802459</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -861,7 +861,7 @@
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>0.00247088765312216</v>
+        <v>0.00187836596605901</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>6.47490007536143</v>
+        <v>6.44474243010147</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2.22978060112986</v>
+        <v>1.85803950282137</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -972,21 +972,21 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.421307488658818</v>
+        <v>-0.422681972205808</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -995,10 +995,10 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -1009,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.52006105112803</v>
+        <v>-1.46575732518987</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
@@ -1018,10 +1018,10 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -1032,7 +1032,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.00790624853901</v>
+        <v>-3.00578433259845</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -1055,7 +1055,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.03584162302847</v>
+        <v>-0.866577072319326</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
@@ -1064,21 +1064,21 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.19571783547909</v>
+        <v>0.19713601645179</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
@@ -1087,10 +1087,10 @@
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -1101,7 +1101,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.706142346697687</v>
+        <v>0.68361931469428</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -1110,10 +1110,10 @@
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5</v>
+        <v>1.50878121751838</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -1133,10 +1133,10 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -1147,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>2.01404748571059</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1.33394593769983</v>
+        <v>1.35310181641373</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
@@ -1179,10 +1179,10 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -1193,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-2.77350098112615</v>
+        <v>-2.75794742656245</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.545544725589981</v>
+        <v>-0.531382975710465</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -1225,10 +1225,10 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.0185667901598089</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
@@ -1248,10 +1248,10 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.21320071635561</v>
+        <v>0.230407806536822</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -1271,10 +1271,10 @@
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>-2.26090736821737</v>
+        <v>-2.29320886985437</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -1308,7 +1308,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-2.16173007636868</v>
+        <v>-2.14741603947789</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.88982236504614</v>
+        <v>1.78920188629657</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
@@ -1340,10 +1340,10 @@
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4.94974746830583</v>
+        <v>4.98203213002363</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>3.21269802057843</v>
+        <v>3.23327388640099</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.866025403784439</v>
+        <v>-0.867034169885047</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
@@ -1409,10 +1409,10 @@
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -1423,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.15470053837925</v>
+        <v>-1.15738979886981</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
@@ -1432,10 +1432,10 @@
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -1446,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.770154046215405</v>
+        <v>-0.777571656209943</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
@@ -1455,10 +1455,10 @@
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -1469,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1.60128153805087</v>
+        <v>1.58487833080878</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
@@ -1478,10 +1478,10 @@
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
@@ -1492,7 +1492,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.314970394174356</v>
+        <v>0.305363820736028</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
@@ -1501,10 +1501,10 @@
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
@@ -1515,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>-0.0106695664730754</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -1524,10 +1524,10 @@
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
@@ -1538,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.123091490979333</v>
+        <v>-0.132405837875069</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
@@ -1547,10 +1547,10 @@
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
@@ -1561,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1.3053354776531</v>
+        <v>1.31781230158572</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
@@ -1570,10 +1570,10 @@
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30">
@@ -1584,7 +1584,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1.24807544150677</v>
+        <v>1.23403119124782</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
@@ -1593,10 +1593,10 @@
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
@@ -1607,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.09108945117996</v>
+        <v>-1.02818033140249</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
@@ -1616,10 +1616,10 @@
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
@@ -1630,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>-2.85773803324704</v>
+        <v>-2.86296783260628</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
@@ -1653,7 +1653,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.85485206700594</v>
+        <v>-1.85802879009695</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
@@ -1662,10 +1662,10 @@
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.222948160685261</v>
+        <v>0.221231259772062</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -1685,10 +1685,10 @@
         <v>6</v>
       </c>
       <c r="F34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35">
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0248755496770252</v>
+        <v>0.0083379668245636</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -1708,21 +1708,21 @@
         <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0672213996993524</v>
+        <v>0.0667037345965071</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -1731,10 +1731,10 @@
         <v>6</v>
       </c>
       <c r="F36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.036898395721925</v>
+        <v>-0.0430570755370188</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -1754,10 +1754,10 @@
         <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
@@ -1768,7 +1768,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.845576726264388</v>
+        <v>-0.842423539174232</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -1777,10 +1777,10 @@
         <v>6</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
@@ -1791,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0943456353049726</v>
+        <v>-0.0317500317500476</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -1800,21 +1800,21 @@
         <v>6</v>
       </c>
       <c r="F39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.254950975679639</v>
+        <v>-0.254000254000381</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -1823,10 +1823,10 @@
         <v>6</v>
       </c>
       <c r="F40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
@@ -1837,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.13994475021931</v>
+        <v>0.163956458945988</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -1846,10 +1846,10 @@
         <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42">
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0806515772719951</v>
+        <v>0.0800640769025435</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -1869,10 +1869,10 @@
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43">
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.16130315454399</v>
+        <v>0.160128153805087</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -1892,10 +1892,10 @@
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44">
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3325349719651</v>
+        <v>0.330112645886763</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -1915,10 +1915,10 @@
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45">
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.292826917562072</v>
+        <v>0.288675134594813</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
@@ -1938,10 +1938,10 @@
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46">
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.142396901477135</v>
+        <v>0.139771311562923</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -1961,10 +1961,10 @@
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47">
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0332546518919704</v>
+        <v>0.03026137663344</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -1984,10 +1984,10 @@
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.156317945905447</v>
+        <v>0.153627466949757</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -2007,10 +2007,10 @@
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49">
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.26946861985961</v>
+        <v>-1.24807544150677</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -2030,10 +2030,10 @@
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50">
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.00352216041000952</v>
+        <v>0</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -2053,10 +2053,10 @@
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.230011342252794</v>
+        <v>0.237880413380021</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -2076,10 +2076,10 @@
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.342175663214512</v>
+        <v>0.339683110243378</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -2099,10 +2099,10 @@
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.213384016306808</v>
+        <v>0.211829636434081</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2122,10 +2122,10 @@
         <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54">
@@ -2136,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.278324969653092</v>
+        <v>-0.277350098112615</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -2145,10 +2145,10 @@
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55">
@@ -2159,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.556649939306183</v>
+        <v>-0.554700196225229</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -2168,10 +2168,10 @@
         <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56">
@@ -2182,7 +2182,7 @@
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>-1.14756324812653</v>
+        <v>-1.14354374979373</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -2191,10 +2191,10 @@
         <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57">
@@ -2205,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>-1.01053253638441</v>
+        <v>-1</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
@@ -2214,10 +2214,10 @@
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58">
@@ -2228,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.491405309392254</v>
+        <v>-0.484182026135042</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -2237,10 +2237,10 @@
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59">
@@ -2251,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.114760309614807</v>
+        <v>-0.104828483672192</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
@@ -2260,10 +2260,10 @@
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60">
@@ -2274,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.539446208269933</v>
+        <v>-0.532181156390174</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
@@ -2283,10 +2283,10 @@
         <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61">
@@ -2297,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>4.38087917247297</v>
+        <v>4.32346015273735</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
@@ -2320,7 +2320,7 @@
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0121548173313837</v>
+        <v>0</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
@@ -2329,10 +2329,10 @@
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63">
@@ -2343,7 +2343,7 @@
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.793758808169083</v>
+        <v>-0.824041924199368</v>
       </c>
       <c r="D63" t="s">
         <v>10</v>
@@ -2352,10 +2352,10 @@
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64">
@@ -2366,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>-1.18083284049145</v>
+        <v>-1.1766968108291</v>
       </c>
       <c r="D64" t="s">
         <v>10</v>
@@ -2375,10 +2375,10 @@
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65">
@@ -2389,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.73637865336168</v>
+        <v>-0.733799385705343</v>
       </c>
       <c r="D65" t="s">
         <v>10</v>
@@ -2398,10 +2398,10 @@
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66">
@@ -2412,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.74963708994867</v>
+        <v>-1.75250328703551</v>
       </c>
       <c r="D66" t="s">
         <v>13</v>
@@ -2421,10 +2421,10 @@
         <v>6</v>
       </c>
       <c r="F66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67">
@@ -2435,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0.608759587435071</v>
+        <v>0.645522907575526</v>
       </c>
       <c r="D67" t="s">
         <v>13</v>
@@ -2444,21 +2444,21 @@
         <v>6</v>
       </c>
       <c r="F67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.162697843363992</v>
+        <v>0.161380726893882</v>
       </c>
       <c r="D68" t="s">
         <v>13</v>
@@ -2467,10 +2467,10 @@
         <v>6</v>
       </c>
       <c r="F68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69">
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.173866707450668</v>
+        <v>0.158478527555277</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -2490,10 +2490,10 @@
         <v>6</v>
       </c>
       <c r="F69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70">
@@ -2504,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>4.16496935126415</v>
+        <v>4.19015680986822</v>
       </c>
       <c r="D70" t="s">
         <v>13</v>
@@ -2527,7 +2527,7 @@
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>-1.44913767461894</v>
+        <v>-1.54341633885262</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
@@ -2536,21 +2536,21 @@
         <v>6</v>
       </c>
       <c r="F71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.387298334620742</v>
+        <v>-0.385854084713155</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
@@ -2559,10 +2559,10 @@
         <v>6</v>
       </c>
       <c r="F72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73">
@@ -2573,7 +2573,7 @@
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.413885549121778</v>
+        <v>-0.37891505617483</v>
       </c>
       <c r="D73" t="s">
         <v>13</v>
@@ -2582,10 +2582,10 @@
         <v>6</v>
       </c>
       <c r="F73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74">
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.907713425025669</v>
+        <v>-0.908391339222708</v>
       </c>
       <c r="D74" t="s">
         <v>13</v>
@@ -2605,10 +2605,10 @@
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75">
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>0.38791172009644</v>
+        <v>0.384911584416402</v>
       </c>
       <c r="D75" t="s">
         <v>13</v>
@@ -2628,10 +2628,10 @@
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76">
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.532506449047602</v>
+        <v>0.526520912445287</v>
       </c>
       <c r="D76" t="s">
         <v>13</v>
@@ -2651,10 +2651,10 @@
         <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77">
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0236692177981122</v>
+        <v>0.0138781845413346</v>
       </c>
       <c r="D77" t="s">
         <v>13</v>
@@ -2674,10 +2674,10 @@
         <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78">
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.313202325481862</v>
+        <v>-0.319179456739213</v>
       </c>
       <c r="D78" t="s">
         <v>13</v>
@@ -2697,10 +2697,10 @@
         <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79">
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.222857610267738</v>
+        <v>-0.229862988571365</v>
       </c>
       <c r="D79" t="s">
         <v>13</v>
@@ -2720,10 +2720,10 @@
         <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G79" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80">
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.205103580386099</v>
+        <v>0.198593489785383</v>
       </c>
       <c r="D80" t="s">
         <v>13</v>
@@ -2743,10 +2743,10 @@
         <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81">
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.759340367496007</v>
+        <v>-0.732243918659764</v>
       </c>
       <c r="D81" t="s">
         <v>13</v>
@@ -2766,10 +2766,10 @@
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G81" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82">
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0.682029151610817</v>
+        <v>0.67305618078742</v>
       </c>
       <c r="D82" t="s">
         <v>13</v>
@@ -2789,10 +2789,10 @@
         <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G82" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.193534240495667</v>
+        <v>0.218717437719594</v>
       </c>
       <c r="D83" t="s">
         <v>13</v>
@@ -2812,10 +2812,10 @@
         <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G83" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84">
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0438872012451088</v>
+        <v>0.0381043028097334</v>
       </c>
       <c r="D84" t="s">
         <v>13</v>
@@ -2835,10 +2835,10 @@
         <v>8</v>
       </c>
       <c r="F84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G84" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85">
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.319624730515571</v>
+        <v>-0.322972047233184</v>
       </c>
       <c r="D85" t="s">
         <v>13</v>
@@ -2858,10 +2858,10 @@
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G85" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86">
@@ -2872,7 +2872,7 @@
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>1.96368437841425</v>
+        <v>1.97353114361673</v>
       </c>
       <c r="D86" t="s">
         <v>13</v>
@@ -2881,10 +2881,10 @@
         <v>8</v>
       </c>
       <c r="F86" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G86" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87">
@@ -2895,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.839181358296689</v>
+        <v>-0.836242010007091</v>
       </c>
       <c r="D87" t="s">
         <v>13</v>
@@ -2904,10 +2904,10 @@
         <v>8</v>
       </c>
       <c r="F87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G87" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88">
@@ -2918,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>-1.15198758393383</v>
+        <v>-1.14389621918392</v>
       </c>
       <c r="D88" t="s">
         <v>13</v>
@@ -2927,10 +2927,10 @@
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G88" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89">
@@ -2941,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.0512043470527298</v>
+        <v>-0.0301511344577766</v>
       </c>
       <c r="D89" t="s">
         <v>13</v>
@@ -2950,10 +2950,10 @@
         <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G89" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90">
@@ -2964,7 +2964,7 @@
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>0.677560226471648</v>
+        <v>0.693435275171721</v>
       </c>
       <c r="D90" t="s">
         <v>13</v>
@@ -2973,10 +2973,10 @@
         <v>8</v>
       </c>
       <c r="F90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G90" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91">
@@ -2987,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>0.482114724568619</v>
+        <v>0.499390237580401</v>
       </c>
       <c r="D91" t="s">
         <v>13</v>
@@ -2996,10 +2996,10 @@
         <v>8</v>
       </c>
       <c r="F91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G91" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92">
@@ -3010,7 +3010,7 @@
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.443706885517998</v>
+        <v>-0.431455497304005</v>
       </c>
       <c r="D92" t="s">
         <v>13</v>
@@ -3019,10 +3019,10 @@
         <v>8</v>
       </c>
       <c r="F92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93">
@@ -3033,7 +3033,7 @@
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>1.64270437832191</v>
+        <v>1.59084099088346</v>
       </c>
       <c r="D93" t="s">
         <v>13</v>
@@ -3042,10 +3042,10 @@
         <v>8</v>
       </c>
       <c r="F93" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G93" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="94">
@@ -3056,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.4754546464964</v>
+        <v>-1.46225231002786</v>
       </c>
       <c r="D94" t="s">
         <v>13</v>
@@ -3065,10 +3065,10 @@
         <v>8</v>
       </c>
       <c r="F94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G94" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95">
@@ -3079,7 +3079,7 @@
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.418678576599064</v>
+        <v>-0.47517590310914</v>
       </c>
       <c r="D95" t="s">
         <v>13</v>
@@ -3088,10 +3088,10 @@
         <v>8</v>
       </c>
       <c r="F95" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G95" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96">
@@ -3102,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.0949425326555084</v>
+        <v>-0.0827837354384715</v>
       </c>
       <c r="D96" t="s">
         <v>13</v>
@@ -3111,10 +3111,10 @@
         <v>8</v>
       </c>
       <c r="F96" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="97">
@@ -3125,7 +3125,7 @@
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0.691454012868151</v>
+        <v>0.701674890777526</v>
       </c>
       <c r="D97" t="s">
         <v>13</v>
@@ -3134,10 +3134,10 @@
         <v>8</v>
       </c>
       <c r="F97" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G97" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="98">
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0.65722670433558</v>
+        <v>0.645547693862359</v>
       </c>
       <c r="D98" t="s">
         <v>15</v>
@@ -3157,10 +3157,10 @@
         <v>6</v>
       </c>
       <c r="F98" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G98" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="99">
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.0675681401094406</v>
+        <v>0.135151208563929</v>
       </c>
       <c r="D99" t="s">
         <v>15</v>
@@ -3180,21 +3180,21 @@
         <v>6</v>
       </c>
       <c r="F99" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G99" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0.422389094945072</v>
+        <v>0.418434250243124</v>
       </c>
       <c r="D100" t="s">
         <v>15</v>
@@ -3203,10 +3203,10 @@
         <v>6</v>
       </c>
       <c r="F100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="101">
@@ -3217,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.121481822959698</v>
+        <v>-0.160087368945452</v>
       </c>
       <c r="D101" t="s">
         <v>15</v>
@@ -3226,10 +3226,10 @@
         <v>6</v>
       </c>
       <c r="F101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G101" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="102">
@@ -3240,7 +3240,7 @@
         <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.91061078986421</v>
+        <v>-0.899515950380844</v>
       </c>
       <c r="D102" t="s">
         <v>15</v>
@@ -3249,10 +3249,10 @@
         <v>6</v>
       </c>
       <c r="F102" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G102" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="103">
@@ -3263,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0936180423418964</v>
+        <v>-0.188321744423152</v>
       </c>
       <c r="D103" t="s">
         <v>15</v>
@@ -3272,21 +3272,21 @@
         <v>6</v>
       </c>
       <c r="F103" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B104" t="n">
         <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.585234995535981</v>
+        <v>-0.583052632451339</v>
       </c>
       <c r="D104" t="s">
         <v>15</v>
@@ -3295,10 +3295,10 @@
         <v>6</v>
       </c>
       <c r="F104" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G104" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105">
@@ -3309,7 +3309,7 @@
         <v>1</v>
       </c>
       <c r="C105" t="n">
-        <v>0.168317352337818</v>
+        <v>0.22306816861101</v>
       </c>
       <c r="D105" t="s">
         <v>15</v>
@@ -3318,10 +3318,10 @@
         <v>6</v>
       </c>
       <c r="F105" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G105" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106">
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.757590695542013</v>
+        <v>-0.75955452531275</v>
       </c>
       <c r="D106" t="s">
         <v>15</v>
@@ -3341,10 +3341,10 @@
         <v>8</v>
       </c>
       <c r="F106" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G106" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="107">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>-1.51518139108403</v>
+        <v>-1.5191090506255</v>
       </c>
       <c r="D107" t="s">
         <v>15</v>
@@ -3364,10 +3364,10 @@
         <v>8</v>
       </c>
       <c r="F107" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G107" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108">
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0.397921378535843</v>
+        <v>0.380719331861533</v>
       </c>
       <c r="D108" t="s">
         <v>15</v>
@@ -3387,10 +3387,10 @@
         <v>8</v>
       </c>
       <c r="F108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G108" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="109">
@@ -3401,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0.943596741938993</v>
+        <v>0.912870929175277</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
@@ -3410,10 +3410,10 @@
         <v>8</v>
       </c>
       <c r="F109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G109" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="110">
@@ -3424,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.303255417974449</v>
+        <v>-0.320446879663701</v>
       </c>
       <c r="D110" t="s">
         <v>15</v>
@@ -3433,10 +3433,10 @@
         <v>8</v>
       </c>
       <c r="F110" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="111">
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.267018649911528</v>
+        <v>-0.287084625881607</v>
       </c>
       <c r="D111" t="s">
         <v>15</v>
@@ -3456,10 +3456,10 @@
         <v>8</v>
       </c>
       <c r="F111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G111" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="112">
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.176382579514814</v>
+        <v>-0.194325082689389</v>
       </c>
       <c r="D112" t="s">
         <v>15</v>
@@ -3479,10 +3479,10 @@
         <v>8</v>
       </c>
       <c r="F112" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G112" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="113">
@@ -3493,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>-2.88332422962332</v>
+        <v>-2.79196802812738</v>
       </c>
       <c r="D113" t="s">
         <v>15</v>
@@ -3516,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0.130242514711562</v>
+        <v>0.105409255338946</v>
       </c>
       <c r="D114" t="s">
         <v>15</v>
@@ -3525,10 +3525,10 @@
         <v>8</v>
       </c>
       <c r="F114" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G114" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="115">
@@ -3539,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>2.22749768478827</v>
+        <v>2.26613480003257</v>
       </c>
       <c r="D115" t="s">
         <v>15</v>
@@ -3562,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>0.830385927978825</v>
+        <v>0.81159685724469</v>
       </c>
       <c r="D116" t="s">
         <v>15</v>
@@ -3571,10 +3571,10 @@
         <v>8</v>
       </c>
       <c r="F116" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G116" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="117">
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>0.989023025659147</v>
+        <v>0.976087727997465</v>
       </c>
       <c r="D117" t="s">
         <v>15</v>
@@ -3594,10 +3594,10 @@
         <v>8</v>
       </c>
       <c r="F117" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G117" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="118">
@@ -3608,7 +3608,7 @@
         <v>1</v>
       </c>
       <c r="C118" t="n">
-        <v>0.879297319479991</v>
+        <v>0.886968593983624</v>
       </c>
       <c r="D118" t="s">
         <v>15</v>
@@ -3617,10 +3617,10 @@
         <v>8</v>
       </c>
       <c r="F118" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G118" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="119">
@@ -3631,7 +3631,7 @@
         <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>1.75859463895998</v>
+        <v>1.77393718796725</v>
       </c>
       <c r="D119" t="s">
         <v>15</v>
@@ -3640,10 +3640,10 @@
         <v>8</v>
       </c>
       <c r="F119" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G119" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="120">
@@ -3654,7 +3654,7 @@
         <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.461847279235685</v>
+        <v>-0.444584396814126</v>
       </c>
       <c r="D120" t="s">
         <v>15</v>
@@ -3663,10 +3663,10 @@
         <v>8</v>
       </c>
       <c r="F120" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G120" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="121">
@@ -3677,7 +3677,7 @@
         <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>-1.09518515834385</v>
+        <v>-1.06600358177805</v>
       </c>
       <c r="D121" t="s">
         <v>15</v>
@@ -3686,10 +3686,10 @@
         <v>8</v>
       </c>
       <c r="F121" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G121" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="122">
@@ -3700,7 +3700,7 @@
         <v>1</v>
       </c>
       <c r="C122" t="n">
-        <v>0.351973272258767</v>
+        <v>0.374201336217069</v>
       </c>
       <c r="D122" t="s">
         <v>15</v>
@@ -3709,10 +3709,10 @@
         <v>8</v>
       </c>
       <c r="F122" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G122" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="123">
@@ -3723,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>0.309915082774868</v>
+        <v>0.335242617200755</v>
       </c>
       <c r="D123" t="s">
         <v>15</v>
@@ -3732,10 +3732,10 @@
         <v>8</v>
       </c>
       <c r="F123" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G123" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124">
@@ -3746,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="C124" t="n">
-        <v>0.204718366108472</v>
+        <v>0.226922807546684</v>
       </c>
       <c r="D124" t="s">
         <v>15</v>
@@ -3755,10 +3755,10 @@
         <v>8</v>
       </c>
       <c r="F124" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G124" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="125">
@@ -3769,7 +3769,7 @@
         <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>3.34652904426926</v>
+        <v>3.26031624304484</v>
       </c>
       <c r="D125" t="s">
         <v>15</v>
@@ -3792,7 +3792,7 @@
         <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.151165919462983</v>
+        <v>-0.123091490979333</v>
       </c>
       <c r="D126" t="s">
         <v>15</v>
@@ -3801,10 +3801,10 @@
         <v>8</v>
       </c>
       <c r="F126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G126" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="127">
@@ -3815,7 +3815,7 @@
         <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>-2.58534424314824</v>
+        <v>-2.64627532372956</v>
       </c>
       <c r="D127" t="s">
         <v>15</v>
@@ -3838,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.963787075134682</v>
+        <v>-0.947740944674703</v>
       </c>
       <c r="D128" t="s">
         <v>15</v>
@@ -3847,10 +3847,10 @@
         <v>8</v>
       </c>
       <c r="F128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G128" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="129">
@@ -3861,7 +3861,7 @@
         <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>-1.14790915527797</v>
+        <v>-1.13982489848257</v>
       </c>
       <c r="D129" t="s">
         <v>15</v>
@@ -3870,10 +3870,10 @@
         <v>8</v>
       </c>
       <c r="F129" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G129" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130">
@@ -3884,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>0.933175225422231</v>
+        <v>0.921869742585667</v>
       </c>
       <c r="D130" t="s">
         <v>16</v>
@@ -3893,10 +3893,10 @@
         <v>6</v>
       </c>
       <c r="F130" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G130" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="131">
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>0.167220131810939</v>
+        <v>0.340056154248439</v>
       </c>
       <c r="D131" t="s">
         <v>16</v>
@@ -3916,21 +3916,21 @@
         <v>6</v>
       </c>
       <c r="F131" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G131" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>0.391809596803858</v>
+        <v>0.388205698212819</v>
       </c>
       <c r="D132" t="s">
         <v>16</v>
@@ -3939,10 +3939,10 @@
         <v>6</v>
       </c>
       <c r="F132" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G132" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="133">
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.21265138819513</v>
+        <v>-0.248176969913951</v>
       </c>
       <c r="D133" t="s">
         <v>16</v>
@@ -3962,10 +3962,10 @@
         <v>6</v>
       </c>
       <c r="F133" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G133" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="134">
@@ -3976,7 +3976,7 @@
         <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>-1.35254894698184</v>
+        <v>-1.34353810154418</v>
       </c>
       <c r="D134" t="s">
         <v>16</v>
@@ -3985,10 +3985,10 @@
         <v>6</v>
       </c>
       <c r="F134" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G134" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="135">
@@ -3999,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.242369714747531</v>
+        <v>-0.495599734747672</v>
       </c>
       <c r="D135" t="s">
         <v>16</v>
@@ -4008,21 +4008,21 @@
         <v>6</v>
       </c>
       <c r="F135" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G135" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B136" t="n">
         <v>1</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.567890834580027</v>
+        <v>-0.565773148517254</v>
       </c>
       <c r="D136" t="s">
         <v>16</v>
@@ -4031,10 +4031,10 @@
         <v>6</v>
       </c>
       <c r="F136" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G136" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="137">
@@ -4045,7 +4045,7 @@
         <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>0.30821801023212</v>
+        <v>0.361694499344293</v>
       </c>
       <c r="D137" t="s">
         <v>16</v>
@@ -4054,10 +4054,10 @@
         <v>6</v>
       </c>
       <c r="F137" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G137" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="138">
@@ -4068,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.778224776537538</v>
+        <v>-0.779994620745303</v>
       </c>
       <c r="D138" t="s">
         <v>16</v>
@@ -4077,10 +4077,10 @@
         <v>8</v>
       </c>
       <c r="F138" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G138" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="139">
@@ -4091,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.913961656166179</v>
+        <v>-0.918959179613719</v>
       </c>
       <c r="D139" t="s">
         <v>16</v>
@@ -4100,10 +4100,10 @@
         <v>8</v>
       </c>
       <c r="F139" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G139" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="140">
@@ -4114,7 +4114,7 @@
         <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.715483695655713</v>
+        <v>-0.728438181156233</v>
       </c>
       <c r="D140" t="s">
         <v>16</v>
@@ -4123,10 +4123,10 @@
         <v>8</v>
       </c>
       <c r="F140" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G140" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="141">
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>0.80312825349341</v>
+        <v>0.775809820602283</v>
       </c>
       <c r="D141" t="s">
         <v>16</v>
@@ -4146,10 +4146,10 @@
         <v>8</v>
       </c>
       <c r="F141" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G141" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="142">
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.201417465398496</v>
+        <v>-0.217162926888798</v>
       </c>
       <c r="D142" t="s">
         <v>16</v>
@@ -4169,10 +4169,10 @@
         <v>8</v>
       </c>
       <c r="F142" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G142" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143">
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.232576855734627</v>
+        <v>-0.250758148594508</v>
       </c>
       <c r="D143" t="s">
         <v>16</v>
@@ -4192,10 +4192,10 @@
         <v>8</v>
       </c>
       <c r="F143" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G143" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="144">
@@ -4206,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.362704639657857</v>
+        <v>-0.378465420178062</v>
       </c>
       <c r="D144" t="s">
         <v>16</v>
@@ -4215,10 +4215,10 @@
         <v>8</v>
       </c>
       <c r="F144" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G144" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="145">
@@ -4229,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>-2.14887955433169</v>
+        <v>-2.07307134199576</v>
       </c>
       <c r="D145" t="s">
         <v>16</v>
@@ -4252,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>0.284007866925781</v>
+        <v>0.261283171779399</v>
       </c>
       <c r="D146" t="s">
         <v>16</v>
@@ -4261,10 +4261,10 @@
         <v>8</v>
       </c>
       <c r="F146" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G146" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="147">
@@ -4275,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>1.46728633985522</v>
+        <v>1.51334253645865</v>
       </c>
       <c r="D147" t="s">
         <v>16</v>
@@ -4284,10 +4284,10 @@
         <v>8</v>
       </c>
       <c r="F147" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G147" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="148">
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>1.54421908583955</v>
+        <v>1.52571459239931</v>
       </c>
       <c r="D148" t="s">
         <v>16</v>
@@ -4307,10 +4307,10 @@
         <v>8</v>
       </c>
       <c r="F148" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G148" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="149">
@@ -4321,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0.8550619696126</v>
+        <v>0.843767283784225</v>
       </c>
       <c r="D149" t="s">
         <v>16</v>
@@ -4330,10 +4330,10 @@
         <v>8</v>
       </c>
       <c r="F149" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G149" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="150">
@@ -4344,7 +4344,7 @@
         <v>1</v>
       </c>
       <c r="C150" t="n">
-        <v>0.964406803634952</v>
+        <v>0.972203589882191</v>
       </c>
       <c r="D150" t="s">
         <v>16</v>
@@ -4353,10 +4353,10 @@
         <v>8</v>
       </c>
       <c r="F150" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G150" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="151">
@@ -4367,7 +4367,7 @@
         <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>1.13261729264105</v>
+        <v>1.14541227543592</v>
       </c>
       <c r="D151" t="s">
         <v>16</v>
@@ -4376,10 +4376,10 @@
         <v>8</v>
       </c>
       <c r="F151" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G151" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="152">
@@ -4390,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="C152" t="n">
-        <v>0.886655584329067</v>
+        <v>0.907942434334549</v>
       </c>
       <c r="D152" t="s">
         <v>16</v>
@@ -4399,10 +4399,10 @@
         <v>8</v>
       </c>
       <c r="F152" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G152" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="153">
@@ -4413,7 +4413,7 @@
         <v>1</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.995268173427449</v>
+        <v>-0.966987556830456</v>
       </c>
       <c r="D153" t="s">
         <v>16</v>
@@ -4422,10 +4422,10 @@
         <v>8</v>
       </c>
       <c r="F153" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G153" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="154">
@@ -4436,7 +4436,7 @@
         <v>1</v>
       </c>
       <c r="C154" t="n">
-        <v>0.24960445858003</v>
+        <v>0.270676965578143</v>
       </c>
       <c r="D154" t="s">
         <v>16</v>
@@ -4445,10 +4445,10 @@
         <v>8</v>
       </c>
       <c r="F154" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G154" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="155">
@@ -4459,7 +4459,7 @@
         <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>0.288218402704222</v>
+        <v>0.312550837879944</v>
       </c>
       <c r="D155" t="s">
         <v>16</v>
@@ -4468,10 +4468,10 @@
         <v>8</v>
       </c>
       <c r="F155" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G155" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="156">
@@ -4482,7 +4482,7 @@
         <v>1</v>
       </c>
       <c r="C156" t="n">
-        <v>0.449477879324661</v>
+        <v>0.471728176524863</v>
       </c>
       <c r="D156" t="s">
         <v>16</v>
@@ -4491,10 +4491,10 @@
         <v>8</v>
       </c>
       <c r="F156" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G156" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="157">
@@ -4505,7 +4505,7 @@
         <v>1</v>
       </c>
       <c r="C157" t="n">
-        <v>2.66297620542226</v>
+        <v>2.58392474405062</v>
       </c>
       <c r="D157" t="s">
         <v>16</v>
@@ -4528,7 +4528,7 @@
         <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.351953738054576</v>
+        <v>-0.325669473639465</v>
       </c>
       <c r="D158" t="s">
         <v>16</v>
@@ -4537,10 +4537,10 @@
         <v>8</v>
       </c>
       <c r="F158" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G158" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="159">
@@ -4551,7 +4551,7 @@
         <v>1</v>
       </c>
       <c r="C159" t="n">
-        <v>-1.81831904058987</v>
+        <v>-1.88626563252536</v>
       </c>
       <c r="D159" t="s">
         <v>16</v>
@@ -4560,10 +4560,10 @@
         <v>8</v>
       </c>
       <c r="F159" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G159" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="160">
@@ -4574,7 +4574,7 @@
         <v>1</v>
       </c>
       <c r="C160" t="n">
-        <v>-1.91365713041491</v>
+        <v>-1.90168645323338</v>
       </c>
       <c r="D160" t="s">
         <v>16</v>
@@ -4583,10 +4583,10 @@
         <v>8</v>
       </c>
       <c r="F160" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G160" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="161">
@@ -4597,7 +4597,7 @@
         <v>1</v>
       </c>
       <c r="C161" t="n">
-        <v>-1.05962648053023</v>
+        <v>-1.0516913328663</v>
       </c>
       <c r="D161" t="s">
         <v>16</v>
@@ -4606,10 +4606,10 @@
         <v>8</v>
       </c>
       <c r="F161" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G161" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="162">
@@ -4620,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.758428308162736</v>
+        <v>-0.764819746282798</v>
       </c>
       <c r="D162" t="s">
         <v>17</v>
@@ -4629,10 +4629,10 @@
         <v>6</v>
       </c>
       <c r="F162" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G162" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="163">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>0.187647649097025</v>
+        <v>0.315639523062999</v>
       </c>
       <c r="D163" t="s">
         <v>17</v>
@@ -4652,21 +4652,21 @@
         <v>6</v>
       </c>
       <c r="F163" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G163" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B164" t="n">
         <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>0.298833309390615</v>
+        <v>0.296226613899671</v>
       </c>
       <c r="D164" t="s">
         <v>17</v>
@@ -4675,10 +4675,10 @@
         <v>6</v>
       </c>
       <c r="F164" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G164" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="165">
@@ -4689,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0783116693081556</v>
+        <v>0.0504952041934665</v>
       </c>
       <c r="D165" t="s">
         <v>17</v>
@@ -4698,10 +4698,10 @@
         <v>6</v>
       </c>
       <c r="F165" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G165" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="166">
@@ -4712,7 +4712,7 @@
         <v>1</v>
       </c>
       <c r="C166" t="n">
-        <v>1.28787628714085</v>
+        <v>1.3052722562828</v>
       </c>
       <c r="D166" t="s">
         <v>17</v>
@@ -4721,10 +4721,10 @@
         <v>6</v>
       </c>
       <c r="F166" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G166" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="167">
@@ -4735,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.318641795155583</v>
+        <v>-0.53868315304732</v>
       </c>
       <c r="D167" t="s">
         <v>17</v>
@@ -4744,21 +4744,21 @@
         <v>6</v>
       </c>
       <c r="F167" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G167" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B168" t="n">
         <v>1</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.507444578254611</v>
+        <v>-0.505552298531881</v>
       </c>
       <c r="D168" t="s">
         <v>17</v>
@@ -4767,10 +4767,10 @@
         <v>6</v>
       </c>
       <c r="F168" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G168" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="169">
@@ -4781,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.132979928126244</v>
+        <v>-0.0861771540672228</v>
       </c>
       <c r="D169" t="s">
         <v>17</v>
@@ -4790,10 +4790,10 @@
         <v>6</v>
       </c>
       <c r="F169" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G169" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="170">
@@ -4804,7 +4804,7 @@
         <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>0.410046900234573</v>
+        <v>0.406465701855701</v>
       </c>
       <c r="D170" t="s">
         <v>17</v>
@@ -4813,10 +4813,10 @@
         <v>8</v>
       </c>
       <c r="F170" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G170" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="171">
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>0.207181591697468</v>
+        <v>0.201093557760189</v>
       </c>
       <c r="D171" t="s">
         <v>17</v>
@@ -4836,10 +4836,10 @@
         <v>8</v>
       </c>
       <c r="F171" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G171" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="172">
@@ -4850,7 +4850,7 @@
         <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>0.798748407243222</v>
+        <v>0.785546175609905</v>
       </c>
       <c r="D172" t="s">
         <v>17</v>
@@ -4859,10 +4859,10 @@
         <v>8</v>
       </c>
       <c r="F172" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G172" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="173">
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>0.0670388072484902</v>
+        <v>0.0462799872555218</v>
       </c>
       <c r="D173" t="s">
         <v>17</v>
@@ -4882,10 +4882,10 @@
         <v>8</v>
       </c>
       <c r="F173" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G173" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="174">
@@ -4896,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.528400404957739</v>
+        <v>-0.540591504223038</v>
       </c>
       <c r="D174" t="s">
         <v>17</v>
@@ -4905,10 +4905,10 @@
         <v>8</v>
       </c>
       <c r="F174" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G174" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="175">
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>0.316491927872717</v>
+        <v>0.300790575078611</v>
       </c>
       <c r="D175" t="s">
         <v>17</v>
@@ -4928,10 +4928,10 @@
         <v>8</v>
       </c>
       <c r="F175" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G175" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="176">
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>0.355210579448333</v>
+        <v>0.341161929208404</v>
       </c>
       <c r="D176" t="s">
         <v>17</v>
@@ -4951,10 +4951,10 @@
         <v>8</v>
       </c>
       <c r="F176" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G176" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="177">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>-2.55300612931285</v>
+        <v>-2.48259418731213</v>
       </c>
       <c r="D177" t="s">
         <v>17</v>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>0.794141063380652</v>
+        <v>0.774873129901969</v>
       </c>
       <c r="D178" t="s">
         <v>17</v>
@@ -4997,10 +4997,10 @@
         <v>8</v>
       </c>
       <c r="F178" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G178" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="179">
@@ -5011,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="C179" t="n">
-        <v>0.316491927872717</v>
+        <v>0.371037821525675</v>
       </c>
       <c r="D179" t="s">
         <v>17</v>
@@ -5020,10 +5020,10 @@
         <v>8</v>
       </c>
       <c r="F179" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G179" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="180">
@@ -5034,7 +5034,7 @@
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>0.872892904373385</v>
+        <v>0.859218544894147</v>
       </c>
       <c r="D180" t="s">
         <v>17</v>
@@ -5043,10 +5043,10 @@
         <v>8</v>
       </c>
       <c r="F180" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G180" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="181">
@@ -5057,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>0.621564043914975</v>
+        <v>0.612901225563407</v>
       </c>
       <c r="D181" t="s">
         <v>17</v>
@@ -5066,10 +5066,10 @@
         <v>8</v>
       </c>
       <c r="F181" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G181" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="182">
@@ -5080,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.578365837730343</v>
+        <v>-0.576340031724183</v>
       </c>
       <c r="D182" t="s">
         <v>17</v>
@@ -5089,10 +5089,10 @@
         <v>8</v>
       </c>
       <c r="F182" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G182" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="183">
@@ -5103,7 +5103,7 @@
         <v>1</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.292226949590068</v>
+        <v>-0.28513664727407</v>
       </c>
       <c r="D183" t="s">
         <v>17</v>
@@ -5112,10 +5112,10 @@
         <v>8</v>
       </c>
       <c r="F183" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G183" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="184">
@@ -5126,7 +5126,7 @@
         <v>1</v>
       </c>
       <c r="C184" t="n">
-        <v>-1.12662427499568</v>
+        <v>-1.11384971894271</v>
       </c>
       <c r="D184" t="s">
         <v>17</v>
@@ -5135,10 +5135,10 @@
         <v>8</v>
       </c>
       <c r="F184" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G184" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="185">
@@ -5149,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.0945573686632816</v>
+        <v>-0.0656217958889712</v>
       </c>
       <c r="D185" t="s">
         <v>17</v>
@@ -5158,10 +5158,10 @@
         <v>8</v>
       </c>
       <c r="F185" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G185" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="186">
@@ -5172,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>0.745301922037718</v>
+        <v>0.76652106997293</v>
       </c>
       <c r="D186" t="s">
         <v>17</v>
@@ -5181,10 +5181,10 @@
         <v>8</v>
       </c>
       <c r="F186" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G186" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="187">
@@ -5195,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.446407761878654</v>
+        <v>-0.426500068250988</v>
       </c>
       <c r="D187" t="s">
         <v>17</v>
@@ -5204,10 +5204,10 @@
         <v>8</v>
       </c>
       <c r="F187" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G187" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="188">
@@ -5218,7 +5218,7 @@
         <v>1</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.501019918052764</v>
+        <v>-0.483743834240801</v>
       </c>
       <c r="D188" t="s">
         <v>17</v>
@@ -5227,10 +5227,10 @@
         <v>8</v>
       </c>
       <c r="F188" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G188" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="189">
@@ -5241,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="C189" t="n">
-        <v>3.60098205318961</v>
+        <v>3.52014550340019</v>
       </c>
       <c r="D189" t="s">
         <v>17</v>
@@ -5264,7 +5264,7 @@
         <v>1</v>
       </c>
       <c r="C190" t="n">
-        <v>-1.12012567619817</v>
+        <v>-1.09871608411492</v>
       </c>
       <c r="D190" t="s">
         <v>17</v>
@@ -5273,10 +5273,10 @@
         <v>8</v>
       </c>
       <c r="F190" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G190" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="191">
@@ -5287,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.446407761878654</v>
+        <v>-0.526105766987681</v>
       </c>
       <c r="D191" t="s">
         <v>17</v>
@@ -5296,10 +5296,10 @@
         <v>8</v>
       </c>
       <c r="F191" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G191" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="192">
@@ -5310,7 +5310,7 @@
         <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>-1.23120412713272</v>
+        <v>-1.21831200310746</v>
       </c>
       <c r="D192" t="s">
         <v>17</v>
@@ -5319,10 +5319,10 @@
         <v>8</v>
       </c>
       <c r="F192" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G192" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="193">
@@ -5333,7 +5333,7 @@
         <v>1</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.876708027194676</v>
+        <v>-0.869051214339379</v>
       </c>
       <c r="D193" t="s">
         <v>17</v>
@@ -5342,10 +5342,10 @@
         <v>8</v>
       </c>
       <c r="F193" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G193" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="194">
@@ -5356,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="C194" t="n">
-        <v>-1.38326936805366</v>
+        <v>-1.38421409798949</v>
       </c>
       <c r="D194" t="s">
         <v>18</v>
@@ -5365,10 +5365,10 @@
         <v>6</v>
       </c>
       <c r="F194" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G194" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="195">
@@ -5379,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="C195" t="n">
-        <v>0.182106369078054</v>
+        <v>0.193194810760745</v>
       </c>
       <c r="D195" t="s">
         <v>18</v>
@@ -5388,21 +5388,21 @@
         <v>6</v>
       </c>
       <c r="F195" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G195" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B196" t="n">
         <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>0.0486699743599632</v>
+        <v>0.0482987026901862</v>
       </c>
       <c r="D196" t="s">
         <v>18</v>
@@ -5411,10 +5411,10 @@
         <v>6</v>
       </c>
       <c r="F196" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G196" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="197">
@@ -5425,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>0.199478772571308</v>
+        <v>0.194673744234394</v>
       </c>
       <c r="D197" t="s">
         <v>18</v>
@@ -5434,10 +5434,10 @@
         <v>6</v>
       </c>
       <c r="F197" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G197" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="198">
@@ -5448,7 +5448,7 @@
         <v>1</v>
       </c>
       <c r="C198" t="n">
-        <v>6.1943030239207</v>
+        <v>6.22288936496789</v>
       </c>
       <c r="D198" t="s">
         <v>18</v>
@@ -5471,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.815475321515005</v>
+        <v>-0.868528889422676</v>
       </c>
       <c r="D199" t="s">
         <v>18</v>
@@ -5480,21 +5480,21 @@
         <v>6</v>
       </c>
       <c r="F199" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G199" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B200" t="n">
         <v>1</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.217944947177034</v>
+        <v>-0.217132222355669</v>
       </c>
       <c r="D200" t="s">
         <v>18</v>
@@ -5503,10 +5503,10 @@
         <v>6</v>
       </c>
       <c r="F200" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G200" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="201">
@@ -5517,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.893269230623576</v>
+        <v>-0.875177600339595</v>
       </c>
       <c r="D201" t="s">
         <v>18</v>
@@ -5526,10 +5526,10 @@
         <v>6</v>
       </c>
       <c r="F201" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G201" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="202">
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>0.0617353792848255</v>
+        <v>0.0612900202459209</v>
       </c>
       <c r="D202" t="s">
         <v>18</v>
@@ -5549,10 +5549,10 @@
         <v>8</v>
       </c>
       <c r="F202" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G202" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="203">
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.392201233103597</v>
+        <v>-0.39297718863561</v>
       </c>
       <c r="D203" t="s">
         <v>18</v>
@@ -5572,10 +5572,10 @@
         <v>8</v>
       </c>
       <c r="F203" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G203" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="204">
@@ -5586,7 +5586,7 @@
         <v>0</v>
       </c>
       <c r="C204" t="n">
-        <v>0.254541489628904</v>
+        <v>0.252705227270177</v>
       </c>
       <c r="D204" t="s">
         <v>18</v>
@@ -5595,10 +5595,10 @@
         <v>8</v>
       </c>
       <c r="F204" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G204" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="205">
@@ -5609,7 +5609,7 @@
         <v>0</v>
       </c>
       <c r="C205" t="n">
-        <v>0.159136796074306</v>
+        <v>0.155988925179455</v>
       </c>
       <c r="D205" t="s">
         <v>18</v>
@@ -5618,10 +5618,10 @@
         <v>8</v>
       </c>
       <c r="F205" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G205" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="206">
@@ -5632,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="C206" t="n">
-        <v>0.0578493404760649</v>
+        <v>0.0558585354500946</v>
       </c>
       <c r="D206" t="s">
         <v>18</v>
@@ -5641,10 +5641,10 @@
         <v>8</v>
       </c>
       <c r="F206" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G206" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="207">
@@ -5655,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="C207" t="n">
-        <v>0.131767228785396</v>
+        <v>0.129453986428386</v>
       </c>
       <c r="D207" t="s">
         <v>18</v>
@@ -5664,10 +5664,10 @@
         <v>8</v>
       </c>
       <c r="F207" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G207" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="208">
@@ -5678,7 +5678,7 @@
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>0.0696813198777005</v>
+        <v>0.0676413357367914</v>
       </c>
       <c r="D208" t="s">
         <v>18</v>
@@ -5687,10 +5687,10 @@
         <v>8</v>
       </c>
       <c r="F208" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G208" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="209">
@@ -5701,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.0280745070852066</v>
+        <v>-0.0218559412776476</v>
       </c>
       <c r="D209" t="s">
         <v>18</v>
@@ -5710,10 +5710,10 @@
         <v>8</v>
       </c>
       <c r="F209" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G209" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="210">
@@ -5724,7 +5724,7 @@
         <v>0</v>
       </c>
       <c r="C210" t="n">
-        <v>0.385537320064101</v>
+        <v>0.382756053757574</v>
       </c>
       <c r="D210" t="s">
         <v>18</v>
@@ -5733,10 +5733,10 @@
         <v>8</v>
       </c>
       <c r="F210" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G210" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="211">
@@ -5747,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.2580441563714</v>
+        <v>-0.244362584017782</v>
       </c>
       <c r="D211" t="s">
         <v>18</v>
@@ -5756,10 +5756,10 @@
         <v>8</v>
       </c>
       <c r="F211" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G211" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="212">
@@ -5770,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.467349292371711</v>
+        <v>-0.469076492001827</v>
       </c>
       <c r="D212" t="s">
         <v>18</v>
@@ -5779,10 +5779,10 @@
         <v>8</v>
       </c>
       <c r="F212" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G212" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="213">
@@ -5793,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.616286309631695</v>
+        <v>-0.617291114232199</v>
       </c>
       <c r="D213" t="s">
         <v>18</v>
@@ -5802,10 +5802,10 @@
         <v>8</v>
       </c>
       <c r="F213" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G213" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="214">
@@ -5816,7 +5816,7 @@
         <v>1</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.244661306563947</v>
+        <v>-0.243804346640004</v>
       </c>
       <c r="D214" t="s">
         <v>18</v>
@@ -5825,10 +5825,10 @@
         <v>8</v>
       </c>
       <c r="F214" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G214" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="215">
@@ -5839,7 +5839,7 @@
         <v>1</v>
       </c>
       <c r="C215" t="n">
-        <v>1.55431888875919</v>
+        <v>1.56321610492709</v>
       </c>
       <c r="D215" t="s">
         <v>18</v>
@@ -5848,10 +5848,10 @@
         <v>8</v>
       </c>
       <c r="F215" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G215" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="216">
@@ -5862,7 +5862,7 @@
         <v>1</v>
       </c>
       <c r="C216" t="n">
-        <v>-1.00876440946478</v>
+        <v>-1.00523107318144</v>
       </c>
       <c r="D216" t="s">
         <v>18</v>
@@ -5871,10 +5871,10 @@
         <v>8</v>
       </c>
       <c r="F216" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G216" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="217">
@@ -5885,7 +5885,7 @@
         <v>1</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.63066942976586</v>
+        <v>-0.620505227994023</v>
       </c>
       <c r="D217" t="s">
         <v>18</v>
@@ -5894,10 +5894,10 @@
         <v>8</v>
       </c>
       <c r="F217" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G217" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="218">
@@ -5908,7 +5908,7 @@
         <v>1</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.229260683075053</v>
+        <v>-0.222198551820258</v>
       </c>
       <c r="D218" t="s">
         <v>18</v>
@@ -5917,10 +5917,10 @@
         <v>8</v>
       </c>
       <c r="F218" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G218" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="219">
@@ -5931,7 +5931,7 @@
         <v>1</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.522202061936138</v>
+        <v>-0.514952425443476</v>
       </c>
       <c r="D219" t="s">
         <v>18</v>
@@ -5940,10 +5940,10 @@
         <v>8</v>
       </c>
       <c r="F219" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G219" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="220">
@@ -5954,7 +5954,7 @@
         <v>1</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.276151583773763</v>
+        <v>-0.269069117598525</v>
       </c>
       <c r="D220" t="s">
         <v>18</v>
@@ -5963,10 +5963,10 @@
         <v>8</v>
       </c>
       <c r="F220" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G220" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="221">
@@ -5977,7 +5977,7 @@
         <v>1</v>
       </c>
       <c r="C221" t="n">
-        <v>0.111261089899772</v>
+        <v>0.0869403120119515</v>
       </c>
       <c r="D221" t="s">
         <v>18</v>
@@ -5986,10 +5986,10 @@
         <v>8</v>
       </c>
       <c r="F221" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G221" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="222">
@@ -6000,7 +6000,7 @@
         <v>1</v>
       </c>
       <c r="C222" t="n">
-        <v>-1.52790936977738</v>
+        <v>-1.52255765676766</v>
       </c>
       <c r="D222" t="s">
         <v>18</v>
@@ -6009,10 +6009,10 @@
         <v>8</v>
       </c>
       <c r="F222" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G222" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="223">
@@ -6023,7 +6023,7 @@
         <v>1</v>
       </c>
       <c r="C223" t="n">
-        <v>1.02264570462494</v>
+        <v>0.972045039317532</v>
       </c>
       <c r="D223" t="s">
         <v>18</v>
@@ -6032,10 +6032,10 @@
         <v>8</v>
       </c>
       <c r="F223" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G223" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="224">
@@ -6046,7 +6046,7 @@
         <v>1</v>
       </c>
       <c r="C224" t="n">
-        <v>1.85213551480527</v>
+        <v>1.86593000292412</v>
       </c>
       <c r="D224" t="s">
         <v>18</v>
@@ -6055,10 +6055,10 @@
         <v>8</v>
       </c>
       <c r="F224" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G224" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="225">
@@ -6069,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="C225" t="n">
-        <v>2.44238256051381</v>
+        <v>2.45550998658836</v>
       </c>
       <c r="D225" t="s">
         <v>18</v>
@@ -6092,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>0.231833234877068</v>
+        <v>0.230045457044116</v>
       </c>
       <c r="D226" t="s">
         <v>20</v>
@@ -6101,10 +6101,10 @@
         <v>6</v>
       </c>
       <c r="F226" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G226" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="227">
@@ -6115,7 +6115,7 @@
         <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.0152220888101521</v>
+        <v>0.0186247975643883</v>
       </c>
       <c r="D227" t="s">
         <v>20</v>
@@ -6124,21 +6124,21 @@
         <v>6</v>
       </c>
       <c r="F227" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G227" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B228" t="n">
         <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0699003503655972</v>
+        <v>0.0693613150673777</v>
       </c>
       <c r="D228" t="s">
         <v>20</v>
@@ -6147,10 +6147,10 @@
         <v>6</v>
       </c>
       <c r="F228" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G228" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="229">
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.0404284164130276</v>
+        <v>-0.0468287565426313</v>
       </c>
       <c r="D229" t="s">
         <v>20</v>
@@ -6170,10 +6170,10 @@
         <v>6</v>
       </c>
       <c r="F229" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G229" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="230">
@@ -6184,7 +6184,7 @@
         <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.861684396980704</v>
+        <v>-0.858471143786814</v>
       </c>
       <c r="D230" t="s">
         <v>20</v>
@@ -6193,10 +6193,10 @@
         <v>6</v>
       </c>
       <c r="F230" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G230" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="231">
@@ -6207,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="C231" t="n">
-        <v>0.0565778949861004</v>
+        <v>-0.0695030081156185</v>
       </c>
       <c r="D231" t="s">
         <v>20</v>
@@ -6216,21 +6216,21 @@
         <v>6</v>
       </c>
       <c r="F231" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G231" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B232" t="n">
         <v>1</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.259807621135332</v>
+        <v>-0.258838788844373</v>
       </c>
       <c r="D232" t="s">
         <v>20</v>
@@ -6239,10 +6239,10 @@
         <v>6</v>
       </c>
       <c r="F232" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G232" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="233">
@@ -6253,7 +6253,7 @@
         <v>1</v>
       </c>
       <c r="C233" t="n">
-        <v>0.15026549423001</v>
+        <v>0.174753010591113</v>
       </c>
       <c r="D233" t="s">
         <v>20</v>
@@ -6262,10 +6262,10 @@
         <v>6</v>
       </c>
       <c r="F233" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G233" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="234">
@@ -6276,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="C234" t="n">
-        <v>0.0844789315215748</v>
+        <v>0.0838623339963139</v>
       </c>
       <c r="D234" t="s">
         <v>20</v>
@@ -6285,10 +6285,10 @@
         <v>8</v>
       </c>
       <c r="F234" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G234" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="235">
@@ -6299,7 +6299,7 @@
         <v>0</v>
       </c>
       <c r="C235" t="n">
-        <v>0.16895786304315</v>
+        <v>0.167724667992628</v>
       </c>
       <c r="D235" t="s">
         <v>20</v>
@@ -6308,10 +6308,10 @@
         <v>8</v>
       </c>
       <c r="F235" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G235" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="236">
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="C236" t="n">
-        <v>0.0953190912657209</v>
+        <v>0.0928547120540947</v>
       </c>
       <c r="D236" t="s">
         <v>20</v>
@@ -6331,10 +6331,10 @@
         <v>8</v>
       </c>
       <c r="F236" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G236" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="237">
@@ -6345,7 +6345,7 @@
         <v>0</v>
       </c>
       <c r="C237" t="n">
-        <v>0.175217446552378</v>
+        <v>0.17090475169345</v>
       </c>
       <c r="D237" t="s">
         <v>20</v>
@@ -6354,10 +6354,10 @@
         <v>8</v>
       </c>
       <c r="F237" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G237" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="238">
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="C238" t="n">
-        <v>0.387131098326607</v>
+        <v>0.384305493493777</v>
       </c>
       <c r="D238" t="s">
         <v>20</v>
@@ -6377,10 +6377,10 @@
         <v>8</v>
       </c>
       <c r="F238" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G238" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="239">
@@ -6391,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>0.447020487661084</v>
+        <v>0.443757760239369</v>
       </c>
       <c r="D239" t="s">
         <v>20</v>
@@ -6400,10 +6400,10 @@
         <v>8</v>
       </c>
       <c r="F239" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G239" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="240">
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="C240" t="n">
-        <v>0.173845002402309</v>
+        <v>0.171021396970386</v>
       </c>
       <c r="D240" t="s">
         <v>20</v>
@@ -6423,10 +6423,10 @@
         <v>8</v>
       </c>
       <c r="F240" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G240" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="241">
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.942404794213406</v>
+        <v>-0.924151136793692</v>
       </c>
       <c r="D241" t="s">
         <v>20</v>
@@ -6446,10 +6446,10 @@
         <v>8</v>
       </c>
       <c r="F241" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G241" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="242">
@@ -6460,7 +6460,7 @@
         <v>0</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.140567905489317</v>
+        <v>-0.144212783348</v>
       </c>
       <c r="D242" t="s">
         <v>20</v>
@@ -6469,10 +6469,10 @@
         <v>8</v>
       </c>
       <c r="F242" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G242" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="243">
@@ -6483,7 +6483,7 @@
         <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>0.249887229127314</v>
+        <v>0.257967554075716</v>
       </c>
       <c r="D243" t="s">
         <v>20</v>
@@ -6492,10 +6492,10 @@
         <v>8</v>
       </c>
       <c r="F243" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G243" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="244">
@@ -6506,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.133322989903335</v>
+        <v>-0.135787547227219</v>
       </c>
       <c r="D244" t="s">
         <v>20</v>
@@ -6515,10 +6515,10 @@
         <v>8</v>
       </c>
       <c r="F244" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G244" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="245">
@@ -6529,7 +6529,7 @@
         <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.170756273236998</v>
+        <v>-0.172266211273047</v>
       </c>
       <c r="D245" t="s">
         <v>20</v>
@@ -6538,10 +6538,10 @@
         <v>8</v>
       </c>
       <c r="F245" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G245" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="246">
@@ -6552,7 +6552,7 @@
         <v>1</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.284580244382771</v>
+        <v>-0.283583462881002</v>
       </c>
       <c r="D246" t="s">
         <v>20</v>
@@ -6561,10 +6561,10 @@
         <v>8</v>
       </c>
       <c r="F246" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G246" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="247">
@@ -6575,7 +6575,7 @@
         <v>1</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.569160488765542</v>
+        <v>-0.567166925762003</v>
       </c>
       <c r="D247" t="s">
         <v>20</v>
@@ -6584,10 +6584,10 @@
         <v>8</v>
       </c>
       <c r="F247" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G247" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="248">
@@ -6598,7 +6598,7 @@
         <v>1</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.321096985936841</v>
+        <v>-0.313991508873052</v>
       </c>
       <c r="D248" t="s">
         <v>20</v>
@@ -6607,10 +6607,10 @@
         <v>8</v>
       </c>
       <c r="F248" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G248" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="249">
@@ -6621,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.590246856368758</v>
+        <v>-0.577920491816703</v>
       </c>
       <c r="D249" t="s">
         <v>20</v>
@@ -6630,10 +6630,10 @@
         <v>8</v>
       </c>
       <c r="F249" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G249" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="250">
@@ -6644,7 +6644,7 @@
         <v>1</v>
       </c>
       <c r="C250" t="n">
-        <v>-1.30411051117308</v>
+        <v>-1.29954268448989</v>
       </c>
       <c r="D250" t="s">
         <v>20</v>
@@ -6653,10 +6653,10 @@
         <v>8</v>
       </c>
       <c r="F250" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G250" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="251">
@@ -6667,7 +6667,7 @@
         <v>1</v>
       </c>
       <c r="C251" t="n">
-        <v>-1.5058571093576</v>
+        <v>-1.50058263742729</v>
       </c>
       <c r="D251" t="s">
         <v>20</v>
@@ -6676,10 +6676,10 @@
         <v>8</v>
       </c>
       <c r="F251" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G251" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="252">
@@ -6690,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.585623567643463</v>
+        <v>-0.57831493196624</v>
       </c>
       <c r="D252" t="s">
         <v>20</v>
@@ -6699,10 +6699,10 @@
         <v>8</v>
       </c>
       <c r="F252" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G252" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="253">
@@ -6713,7 +6713,7 @@
         <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>3.17463516422736</v>
+        <v>3.12504991345565</v>
       </c>
       <c r="D253" t="s">
         <v>20</v>
@@ -6736,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="C254" t="n">
-        <v>0.473524560218994</v>
+        <v>0.487660652222378</v>
       </c>
       <c r="D254" t="s">
         <v>20</v>
@@ -6745,10 +6745,10 @@
         <v>8</v>
       </c>
       <c r="F254" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G254" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="255">
@@ -6759,7 +6759,7 @@
         <v>1</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.841783477280644</v>
+        <v>-0.872326452289642</v>
       </c>
       <c r="D255" t="s">
         <v>20</v>
@@ -6768,10 +6768,10 @@
         <v>8</v>
       </c>
       <c r="F255" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G255" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="256">
@@ -6782,7 +6782,7 @@
         <v>1</v>
       </c>
       <c r="C256" t="n">
-        <v>0.449118950312992</v>
+        <v>0.459170416846553</v>
       </c>
       <c r="D256" t="s">
         <v>20</v>
@@ -6791,10 +6791,10 @@
         <v>8</v>
       </c>
       <c r="F256" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G256" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="257">
@@ -6805,7 +6805,7 @@
         <v>1</v>
       </c>
       <c r="C257" t="n">
-        <v>0.575218709475107</v>
+        <v>0.582524315771465</v>
       </c>
       <c r="D257" t="s">
         <v>20</v>
@@ -6814,10 +6814,10 @@
         <v>8</v>
       </c>
       <c r="F257" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G257" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="258">
@@ -6828,7 +6828,7 @@
         <v>0</v>
       </c>
       <c r="C258" t="n">
-        <v>-2.16123415316931</v>
+        <v>-2.15643507127525</v>
       </c>
       <c r="D258" t="s">
         <v>21</v>
@@ -6851,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>-1.1440558436359</v>
+        <v>-1.44736910011475</v>
       </c>
       <c r="D259" t="s">
         <v>21</v>
@@ -6860,21 +6860,21 @@
         <v>6</v>
       </c>
       <c r="F259" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G259" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B260" t="n">
         <v>0</v>
       </c>
       <c r="C260" t="n">
-        <v>0.529399389006229</v>
+        <v>0.532773901882729</v>
       </c>
       <c r="D260" t="s">
         <v>21</v>
@@ -6883,10 +6883,10 @@
         <v>6</v>
       </c>
       <c r="F260" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G260" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="261">
@@ -6897,7 +6897,7 @@
         <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>0.564621926272927</v>
+        <v>0.640787083523648</v>
       </c>
       <c r="D261" t="s">
         <v>21</v>
@@ -6906,10 +6906,10 @@
         <v>6</v>
       </c>
       <c r="F261" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G261" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="262">
@@ -6920,7 +6920,7 @@
         <v>1</v>
       </c>
       <c r="C262" t="n">
-        <v>2.60604669263505</v>
+        <v>2.58989938678678</v>
       </c>
       <c r="D262" t="s">
         <v>21</v>
@@ -6943,7 +6943,7 @@
         <v>1</v>
       </c>
       <c r="C263" t="n">
-        <v>1.37951870838475</v>
+        <v>1.73830429432988</v>
       </c>
       <c r="D263" t="s">
         <v>21</v>
@@ -6952,21 +6952,21 @@
         <v>6</v>
       </c>
       <c r="F263" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G263" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B264" t="n">
         <v>1</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.638357266740185</v>
+        <v>-0.639866611409771</v>
       </c>
       <c r="D264" t="s">
         <v>21</v>
@@ -6975,10 +6975,10 @@
         <v>6</v>
       </c>
       <c r="F264" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G264" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="265">
@@ -6989,7 +6989,7 @@
         <v>1</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.680829100074619</v>
+        <v>-0.769591487722079</v>
       </c>
       <c r="D265" t="s">
         <v>21</v>
@@ -6998,10 +6998,10 @@
         <v>6</v>
       </c>
       <c r="F265" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G265" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="266">
@@ -7012,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.684331687966391</v>
+        <v>-0.681934721974886</v>
       </c>
       <c r="D266" t="s">
         <v>21</v>
@@ -7021,10 +7021,10 @@
         <v>8</v>
       </c>
       <c r="F266" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G266" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="267">
@@ -7035,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="C267" t="n">
-        <v>0.0926163186721431</v>
+        <v>0.102546574733065</v>
       </c>
       <c r="D267" t="s">
         <v>21</v>
@@ -7044,10 +7044,10 @@
         <v>8</v>
       </c>
       <c r="F267" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G267" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="268">
@@ -7058,7 +7058,7 @@
         <v>0</v>
       </c>
       <c r="C268" t="n">
-        <v>0.013727240228602</v>
+        <v>0.0335761167575957</v>
       </c>
       <c r="D268" t="s">
         <v>21</v>
@@ -7067,10 +7067,10 @@
         <v>8</v>
       </c>
       <c r="F268" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G268" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="269">
@@ -7081,7 +7081,7 @@
         <v>0</v>
       </c>
       <c r="C269" t="n">
-        <v>1.75243411925739</v>
+        <v>1.79322412661785</v>
       </c>
       <c r="D269" t="s">
         <v>21</v>
@@ -7090,10 +7090,10 @@
         <v>8</v>
       </c>
       <c r="F269" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G269" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="270">
@@ -7104,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.584982784551831</v>
+        <v>-0.565031804026721</v>
       </c>
       <c r="D270" t="s">
         <v>21</v>
@@ -7113,10 +7113,10 @@
         <v>8</v>
       </c>
       <c r="F270" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G270" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="271">
@@ -7127,7 +7127,7 @@
         <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>0.521195651398016</v>
+        <v>0.548439313402065</v>
       </c>
       <c r="D271" t="s">
         <v>21</v>
@@ -7136,10 +7136,10 @@
         <v>8</v>
       </c>
       <c r="F271" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G271" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="272">
@@ -7150,7 +7150,7 @@
         <v>0</v>
       </c>
       <c r="C272" t="n">
-        <v>0.528750398044002</v>
+        <v>0.553133980780464</v>
       </c>
       <c r="D272" t="s">
         <v>21</v>
@@ -7159,10 +7159,10 @@
         <v>8</v>
       </c>
       <c r="F272" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G272" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="273">
@@ -7173,7 +7173,7 @@
         <v>0</v>
       </c>
       <c r="C273" t="n">
-        <v>-1.06799933090391</v>
+        <v>-1.12638069031875</v>
       </c>
       <c r="D273" t="s">
         <v>21</v>
@@ -7182,10 +7182,10 @@
         <v>8</v>
       </c>
       <c r="F273" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G273" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="274">
@@ -7196,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="C274" t="n">
-        <v>1.576150470658</v>
+        <v>1.61168127077569</v>
       </c>
       <c r="D274" t="s">
         <v>21</v>
@@ -7205,10 +7205,10 @@
         <v>8</v>
       </c>
       <c r="F274" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G274" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="275">
@@ -7219,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.859583872828071</v>
+        <v>-0.949264680566653</v>
       </c>
       <c r="D275" t="s">
         <v>21</v>
@@ -7228,10 +7228,10 @@
         <v>8</v>
       </c>
       <c r="F275" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G275" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="276">
@@ -7242,7 +7242,7 @@
         <v>0</v>
       </c>
       <c r="C276" t="n">
-        <v>-2.21451960867433</v>
+        <v>-2.20192885684255</v>
       </c>
       <c r="D276" t="s">
         <v>21</v>
@@ -7265,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="C277" t="n">
-        <v>-1.25825965094969</v>
+        <v>-1.24997652701177</v>
       </c>
       <c r="D277" t="s">
         <v>21</v>
@@ -7274,10 +7274,10 @@
         <v>8</v>
       </c>
       <c r="F277" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G277" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="278">
@@ -7288,7 +7288,7 @@
         <v>1</v>
       </c>
       <c r="C278" t="n">
-        <v>0.642249828985439</v>
+        <v>0.635803492218051</v>
       </c>
       <c r="D278" t="s">
         <v>21</v>
@@ -7297,10 +7297,10 @@
         <v>8</v>
       </c>
       <c r="F278" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G278" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="279">
@@ -7311,7 +7311,7 @@
         <v>1</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.086921029486751</v>
+        <v>-0.0956095477019626</v>
       </c>
       <c r="D279" t="s">
         <v>21</v>
@@ -7320,10 +7320,10 @@
         <v>8</v>
       </c>
       <c r="F279" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G279" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="280">
@@ -7334,7 +7334,7 @@
         <v>1</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.0128831060205046</v>
+        <v>-0.0313047739053046</v>
       </c>
       <c r="D280" t="s">
         <v>21</v>
@@ -7343,10 +7343,10 @@
         <v>8</v>
       </c>
       <c r="F280" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G280" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="281">
@@ -7357,7 +7357,7 @@
         <v>1</v>
       </c>
       <c r="C281" t="n">
-        <v>-1.64467104650075</v>
+        <v>-1.67191686431723</v>
       </c>
       <c r="D281" t="s">
         <v>21</v>
@@ -7366,10 +7366,10 @@
         <v>8</v>
       </c>
       <c r="F281" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G281" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="282">
@@ -7380,7 +7380,7 @@
         <v>1</v>
       </c>
       <c r="C282" t="n">
-        <v>0.549010224054233</v>
+        <v>0.526808773094978</v>
       </c>
       <c r="D282" t="s">
         <v>21</v>
@@ -7389,10 +7389,10 @@
         <v>8</v>
       </c>
       <c r="F282" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G282" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="283">
@@ -7403,7 +7403,7 @@
         <v>1</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.489145576428093</v>
+        <v>-0.511338724212293</v>
       </c>
       <c r="D283" t="s">
         <v>21</v>
@@ -7412,10 +7412,10 @@
         <v>8</v>
       </c>
       <c r="F283" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G283" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="284">
@@ -7426,7 +7426,7 @@
         <v>1</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.496235756273238</v>
+        <v>-0.515715808730506</v>
       </c>
       <c r="D284" t="s">
         <v>21</v>
@@ -7435,10 +7435,10 @@
         <v>8</v>
       </c>
       <c r="F284" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G284" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="285">
@@ -7449,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="C285" t="n">
-        <v>1.00232445711806</v>
+        <v>1.05018376890627</v>
       </c>
       <c r="D285" t="s">
         <v>21</v>
@@ -7458,10 +7458,10 @@
         <v>8</v>
       </c>
       <c r="F285" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G285" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="286">
@@ -7472,7 +7472,7 @@
         <v>1</v>
       </c>
       <c r="C286" t="n">
-        <v>-1.47922767283156</v>
+        <v>-1.50265494230011</v>
       </c>
       <c r="D286" t="s">
         <v>21</v>
@@ -7481,10 +7481,10 @@
         <v>8</v>
       </c>
       <c r="F286" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G286" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="287">
@@ -7495,7 +7495,7 @@
         <v>1</v>
       </c>
       <c r="C287" t="n">
-        <v>0.806725167094094</v>
+        <v>0.885049227579525</v>
       </c>
       <c r="D287" t="s">
         <v>21</v>
@@ -7504,10 +7504,10 @@
         <v>8</v>
       </c>
       <c r="F287" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G287" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="288">
@@ -7518,7 +7518,7 @@
         <v>1</v>
       </c>
       <c r="C288" t="n">
-        <v>2.07834134377515</v>
+        <v>2.05297371094671</v>
       </c>
       <c r="D288" t="s">
         <v>21</v>
@@ -7541,7 +7541,7 @@
         <v>1</v>
       </c>
       <c r="C289" t="n">
-        <v>1.18088502966036</v>
+        <v>1.16541864705629</v>
       </c>
       <c r="D289" t="s">
         <v>21</v>
@@ -7550,10 +7550,10 @@
         <v>8</v>
       </c>
       <c r="F289" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G289" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -7595,7 +7595,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>2.07834134377515</v>
+        <v>2.05297371094671</v>
       </c>
       <c r="E2" t="s">
         <v>27</v>
@@ -7612,7 +7612,7 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>3.17463516422736</v>
+        <v>3.12504991345565</v>
       </c>
       <c r="E3" t="s">
         <v>27</v>
@@ -7629,7 +7629,7 @@
         <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>2.44238256051381</v>
+        <v>2.45550998658836</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -7646,7 +7646,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>3.34652904426926</v>
+        <v>3.26031624304484</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
@@ -7663,7 +7663,7 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.58534424314824</v>
+        <v>-2.64627532372956</v>
       </c>
       <c r="E6" t="s">
         <v>34</v>
@@ -7680,7 +7680,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>2.66297620542226</v>
+        <v>2.58392474405062</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
@@ -7697,7 +7697,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>3.60098205318961</v>
+        <v>3.52014550340019</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -7714,7 +7714,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>4.38087917247297</v>
+        <v>4.32346015273735</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
@@ -7731,7 +7731,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.85773803324704</v>
+        <v>-2.86296783260628</v>
       </c>
       <c r="E10" t="s">
         <v>34</v>
@@ -7748,7 +7748,7 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>2.60604669263505</v>
+        <v>2.58989938678678</v>
       </c>
       <c r="E11" t="s">
         <v>27</v>
@@ -7765,7 +7765,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>6.1943030239207</v>
+        <v>6.22288936496789</v>
       </c>
       <c r="E12" t="s">
         <v>27</v>
@@ -7782,7 +7782,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.00790624853901</v>
+        <v>-3.00578433259845</v>
       </c>
       <c r="E13" t="s">
         <v>34</v>
@@ -7799,7 +7799,7 @@
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>4.16496935126415</v>
+        <v>4.19015680986822</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -7853,7 +7853,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0636710147772251</v>
+        <v>0.0729817116141384</v>
       </c>
       <c r="E2" t="s">
         <v>48</v>
@@ -7879,7 +7879,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>0.779011472946283</v>
+        <v>0.744608080581225</v>
       </c>
       <c r="E3" t="s">
         <v>50</v>
@@ -7891,7 +7891,7 @@
         <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -7942,7 +7942,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.518683012982283</v>
+        <v>0.619425926200538</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -7954,7 +7954,7 @@
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -7968,7 +7968,7 @@
         <v>54</v>
       </c>
       <c r="D3" t="n">
-        <v>0.160439453031613</v>
+        <v>0.145055101131499</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
@@ -7980,7 +7980,7 @@
         <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -8025,7 +8025,7 @@
         <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.05012232250847</v>
+        <v>-1.04619661784202</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -8034,10 +8034,10 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -8048,7 +8048,7 @@
         <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>2.19169084770864</v>
+        <v>1.90841290107645</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -8057,21 +8057,21 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.316623793430652</v>
+        <v>-0.315440148938256</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -8080,10 +8080,10 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -8094,7 +8094,7 @@
         <v>55</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.227878804384393</v>
+        <v>-0.198994465894324</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -8103,10 +8103,10 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -8117,7 +8117,7 @@
         <v>57</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.84082441550859</v>
+        <v>-0.837572106479999</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -8126,10 +8126,10 @@
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -8140,7 +8140,7 @@
         <v>57</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.875412866823603</v>
+        <v>-1.14715411348299</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -8149,21 +8149,21 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>0.841515425549458</v>
+        <v>0.843495671678671</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -8172,10 +8172,10 @@
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -8186,7 +8186,7 @@
         <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>0.270420052310922</v>
+        <v>0.33729801662092</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -8195,10 +8195,10 @@
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -8209,7 +8209,7 @@
         <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>2.63181998579447</v>
+        <v>2.60278527359852</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -8232,7 +8232,7 @@
         <v>58</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0689757700500649</v>
+        <v>0.560017323825857</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -8241,21 +8241,21 @@
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
         <v>58</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.54381922398066</v>
+        <v>-0.546358364708153</v>
       </c>
       <c r="D12" t="s">
         <v>56</v>
@@ -8264,10 +8264,10 @@
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -8278,7 +8278,7 @@
         <v>58</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.410437070821644</v>
+        <v>-0.533953699113986</v>
       </c>
       <c r="D13" t="s">
         <v>56</v>
@@ -8287,10 +8287,10 @@
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -8301,7 +8301,7 @@
         <v>59</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.00997530925923</v>
+        <v>-1.00619968741064</v>
       </c>
       <c r="D14" t="s">
         <v>56</v>
@@ -8310,10 +8310,10 @@
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -8324,7 +8324,7 @@
         <v>59</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.13940581621962</v>
+        <v>-1.21352248265963</v>
       </c>
       <c r="D15" t="s">
         <v>56</v>
@@ -8333,21 +8333,21 @@
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.304519013485094</v>
+        <v>-0.303380620664908</v>
       </c>
       <c r="D16" t="s">
         <v>56</v>
@@ -8356,10 +8356,10 @@
         <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -8370,7 +8370,7 @@
         <v>59</v>
       </c>
       <c r="C17" t="n">
-        <v>0.409952317870701</v>
+        <v>0.439248276120844</v>
       </c>
       <c r="D17" t="s">
         <v>56</v>
@@ -8379,10 +8379,10 @@
         <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
@@ -8393,7 +8393,7 @@
         <v>60</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.878595370213959</v>
+        <v>-0.875310890043564</v>
       </c>
       <c r="D18" t="s">
         <v>56</v>
@@ -8402,10 +8402,10 @@
         <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -8416,7 +8416,7 @@
         <v>60</v>
       </c>
       <c r="C19" t="n">
-        <v>1.02658887183694</v>
+        <v>0.838876376459745</v>
       </c>
       <c r="D19" t="s">
         <v>56</v>
@@ -8425,21 +8425,21 @@
         <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
         <v>60</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.264906471413009</v>
+        <v>-0.263916163380594</v>
       </c>
       <c r="D20" t="s">
         <v>56</v>
@@ -8448,10 +8448,10 @@
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
@@ -8462,7 +8462,7 @@
         <v>60</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0342908428997843</v>
+        <v>-0.00974769994820156</v>
       </c>
       <c r="D21" t="s">
         <v>56</v>
@@ -8471,10 +8471,10 @@
         <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
@@ -8485,7 +8485,7 @@
         <v>55</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.308334919422389</v>
+        <v>-0.307254933899513</v>
       </c>
       <c r="D22" t="s">
         <v>56</v>
@@ -8494,10 +8494,10 @@
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -8508,7 +8508,7 @@
         <v>55</v>
       </c>
       <c r="C23" t="n">
-        <v>1.00494344108038</v>
+        <v>1.01280330063173</v>
       </c>
       <c r="D23" t="s">
         <v>56</v>
@@ -8517,10 +8517,10 @@
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -8531,7 +8531,7 @@
         <v>55</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.27129744084482</v>
+        <v>-1.26684454645987</v>
       </c>
       <c r="D24" t="s">
         <v>56</v>
@@ -8540,10 +8540,10 @@
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -8554,7 +8554,7 @@
         <v>55</v>
       </c>
       <c r="C25" t="n">
-        <v>0.475092889740804</v>
+        <v>0.492365963917331</v>
       </c>
       <c r="D25" t="s">
         <v>56</v>
@@ -8563,10 +8563,10 @@
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
@@ -8577,7 +8577,7 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00249200724453483</v>
+        <v>0.0124163932296576</v>
       </c>
       <c r="D26" t="s">
         <v>56</v>
@@ -8586,10 +8586,10 @@
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
@@ -8600,7 +8600,7 @@
         <v>55</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.405730617074209</v>
+        <v>-0.39570716013759</v>
       </c>
       <c r="D27" t="s">
         <v>56</v>
@@ -8609,10 +8609,10 @@
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
@@ -8623,7 +8623,7 @@
         <v>55</v>
       </c>
       <c r="C28" t="n">
-        <v>0.628155712228227</v>
+        <v>0.640512615220348</v>
       </c>
       <c r="D28" t="s">
         <v>56</v>
@@ -8632,10 +8632,10 @@
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
@@ -8646,7 +8646,7 @@
         <v>55</v>
       </c>
       <c r="C29" t="n">
-        <v>0.251528364089173</v>
+        <v>0.220099614062603</v>
       </c>
       <c r="D29" t="s">
         <v>56</v>
@@ -8655,10 +8655,10 @@
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30">
@@ -8669,7 +8669,7 @@
         <v>55</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.367555310427787</v>
+        <v>-0.355334527259351</v>
       </c>
       <c r="D30" t="s">
         <v>56</v>
@@ -8678,10 +8678,10 @@
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
@@ -8692,7 +8692,7 @@
         <v>55</v>
       </c>
       <c r="C31" t="n">
-        <v>0.207181591697468</v>
+        <v>0.158488357936216</v>
       </c>
       <c r="D31" t="s">
         <v>56</v>
@@ -8701,10 +8701,10 @@
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
@@ -8715,7 +8715,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>0.22071738786191</v>
+        <v>0.23067328480185</v>
       </c>
       <c r="D32" t="s">
         <v>56</v>
@@ -8724,10 +8724,10 @@
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
@@ -8738,7 +8738,7 @@
         <v>55</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.815777517308781</v>
+        <v>-0.812920144195702</v>
       </c>
       <c r="D33" t="s">
         <v>56</v>
@@ -8747,10 +8747,10 @@
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -8761,7 +8761,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>0.897534793952737</v>
+        <v>0.905232158411162</v>
       </c>
       <c r="D34" t="s">
         <v>56</v>
@@ -8770,10 +8770,10 @@
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35">
@@ -8784,7 +8784,7 @@
         <v>57</v>
       </c>
       <c r="C35" t="n">
-        <v>0.250221821344399</v>
+        <v>0.260186488645124</v>
       </c>
       <c r="D35" t="s">
         <v>56</v>
@@ -8793,10 +8793,10 @@
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
@@ -8807,7 +8807,7 @@
         <v>57</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.420856047003488</v>
+        <v>-0.403605817571106</v>
       </c>
       <c r="D36" t="s">
         <v>56</v>
@@ -8816,10 +8816,10 @@
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37">
@@ -8830,7 +8830,7 @@
         <v>57</v>
       </c>
       <c r="C37" t="n">
-        <v>1.75911496634676</v>
+        <v>1.79805514148644</v>
       </c>
       <c r="D37" t="s">
         <v>56</v>
@@ -8839,10 +8839,10 @@
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
@@ -8853,7 +8853,7 @@
         <v>57</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0676600878880995</v>
+        <v>0.088714604093828</v>
       </c>
       <c r="D38" t="s">
         <v>56</v>
@@ -8862,10 +8862,10 @@
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
@@ -8876,7 +8876,7 @@
         <v>57</v>
       </c>
       <c r="C39" t="n">
-        <v>0.078127139911176</v>
+        <v>0.102438801109246</v>
       </c>
       <c r="D39" t="s">
         <v>56</v>
@@ -8885,10 +8885,10 @@
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
@@ -8899,7 +8899,7 @@
         <v>57</v>
       </c>
       <c r="C40" t="n">
-        <v>0.586822187142746</v>
+        <v>0.610191403417106</v>
       </c>
       <c r="D40" t="s">
         <v>56</v>
@@ -8908,10 +8908,10 @@
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
@@ -8922,7 +8922,7 @@
         <v>57</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.05766606353704</v>
+        <v>-1.11255753763524</v>
       </c>
       <c r="D41" t="s">
         <v>56</v>
@@ -8931,10 +8931,10 @@
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42">
@@ -8945,7 +8945,7 @@
         <v>57</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0844902859669919</v>
+        <v>-0.0564188923888578</v>
       </c>
       <c r="D42" t="s">
         <v>56</v>
@@ -8954,10 +8954,10 @@
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43">
@@ -8968,7 +8968,7 @@
         <v>57</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.0896680040243</v>
+        <v>-1.17064231524457</v>
       </c>
       <c r="D43" t="s">
         <v>56</v>
@@ -8977,10 +8977,10 @@
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44">
@@ -8991,7 +8991,7 @@
         <v>57</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.197447581070398</v>
+        <v>-0.178869085202582</v>
       </c>
       <c r="D44" t="s">
         <v>56</v>
@@ -9000,10 +9000,10 @@
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45">
@@ -9014,7 +9014,7 @@
         <v>57</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.54483400201215</v>
+        <v>-0.534730541790262</v>
       </c>
       <c r="D45" t="s">
         <v>56</v>
@@ -9023,10 +9023,10 @@
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46">
@@ -9037,7 +9037,7 @@
         <v>58</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.540604773496092</v>
+        <v>-0.545163092296972</v>
       </c>
       <c r="D46" t="s">
         <v>56</v>
@@ -9046,10 +9046,10 @@
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47">
@@ -9060,7 +9060,7 @@
         <v>58</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.156319452577183</v>
+        <v>-0.173169452847274</v>
       </c>
       <c r="D47" t="s">
         <v>56</v>
@@ -9069,10 +9069,10 @@
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
@@ -9083,7 +9083,7 @@
         <v>58</v>
       </c>
       <c r="C48" t="n">
-        <v>0.014217388551054</v>
+        <v>-0.0233332008241741</v>
       </c>
       <c r="D48" t="s">
         <v>56</v>
@@ -9092,10 +9092,10 @@
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49">
@@ -9106,7 +9106,7 @@
         <v>58</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.58969123533704</v>
+        <v>-1.64186537972323</v>
       </c>
       <c r="D49" t="s">
         <v>56</v>
@@ -9115,10 +9115,10 @@
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50">
@@ -9129,7 +9129,7 @@
         <v>58</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.459086644566205</v>
+        <v>-0.496851066372107</v>
       </c>
       <c r="D50" t="s">
         <v>56</v>
@@ -9138,10 +9138,10 @@
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51">
@@ -9152,7 +9152,7 @@
         <v>58</v>
       </c>
       <c r="C51" t="n">
-        <v>0.285568797653058</v>
+        <v>0.23514201465598</v>
       </c>
       <c r="D51" t="s">
         <v>56</v>
@@ -9161,10 +9161,10 @@
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
@@ -9175,7 +9175,7 @@
         <v>58</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.563788842646982</v>
+        <v>-0.601656837596187</v>
       </c>
       <c r="D52" t="s">
         <v>56</v>
@@ -9184,10 +9184,10 @@
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
@@ -9198,7 +9198,7 @@
         <v>58</v>
       </c>
       <c r="C53" t="n">
-        <v>0.07125479881602</v>
+        <v>0.194404447643766</v>
       </c>
       <c r="D53" t="s">
         <v>56</v>
@@ -9207,10 +9207,10 @@
         <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54">
@@ -9221,7 +9221,7 @@
         <v>58</v>
       </c>
       <c r="C54" t="n">
-        <v>0.474548797165743</v>
+        <v>0.413885549121778</v>
       </c>
       <c r="D54" t="s">
         <v>56</v>
@@ -9230,10 +9230,10 @@
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55">
@@ -9244,7 +9244,7 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>1.33429558903412</v>
+        <v>1.49231186725323</v>
       </c>
       <c r="D55" t="s">
         <v>56</v>
@@ -9253,10 +9253,10 @@
         <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56">
@@ -9267,7 +9267,7 @@
         <v>58</v>
       </c>
       <c r="C56" t="n">
-        <v>0.758389794509103</v>
+        <v>0.713531690840257</v>
       </c>
       <c r="D56" t="s">
         <v>56</v>
@@ -9276,10 +9276,10 @@
         <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57">
@@ -9290,7 +9290,7 @@
         <v>58</v>
       </c>
       <c r="C57" t="n">
-        <v>0.667147794517059</v>
+        <v>0.637549998500233</v>
       </c>
       <c r="D57" t="s">
         <v>56</v>
@@ -9299,10 +9299,10 @@
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58">
@@ -9313,7 +9313,7 @@
         <v>59</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.330386031147603</v>
+        <v>-0.329228808568765</v>
       </c>
       <c r="D58" t="s">
         <v>56</v>
@@ -9322,10 +9322,10 @@
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59">
@@ -9336,7 +9336,7 @@
         <v>59</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.660772062295206</v>
+        <v>-0.65845761713753</v>
       </c>
       <c r="D59" t="s">
         <v>56</v>
@@ -9345,10 +9345,10 @@
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60">
@@ -9359,7 +9359,7 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>0.840076591435116</v>
+        <v>0.852588890990637</v>
       </c>
       <c r="D60" t="s">
         <v>56</v>
@@ -9368,10 +9368,10 @@
         <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61">
@@ -9382,7 +9382,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="n">
-        <v>0.135970952099224</v>
+        <v>0.153167916213497</v>
       </c>
       <c r="D61" t="s">
         <v>56</v>
@@ -9391,10 +9391,10 @@
         <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62">
@@ -9405,7 +9405,7 @@
         <v>59</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.853525302055919</v>
+        <v>-0.845900640126988</v>
       </c>
       <c r="D62" t="s">
         <v>56</v>
@@ -9414,10 +9414,10 @@
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63">
@@ -9428,7 +9428,7 @@
         <v>59</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.604229913640228</v>
+        <v>-0.594085334943937</v>
       </c>
       <c r="D63" t="s">
         <v>56</v>
@@ -9437,10 +9437,10 @@
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64">
@@ -9451,7 +9451,7 @@
         <v>59</v>
       </c>
       <c r="C64" t="n">
-        <v>-1.54964784732023</v>
+        <v>-1.54421999229883</v>
       </c>
       <c r="D64" t="s">
         <v>56</v>
@@ -9460,10 +9460,10 @@
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65">
@@ -9474,7 +9474,7 @@
         <v>59</v>
       </c>
       <c r="C65" t="n">
-        <v>0.825478136662565</v>
+        <v>0.787913672609744</v>
       </c>
       <c r="D65" t="s">
         <v>56</v>
@@ -9483,10 +9483,10 @@
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66">
@@ -9497,7 +9497,7 @@
         <v>59</v>
       </c>
       <c r="C66" t="n">
-        <v>0.360089232240269</v>
+        <v>0.375834035042575</v>
       </c>
       <c r="D66" t="s">
         <v>56</v>
@@ -9506,10 +9506,10 @@
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67">
@@ -9520,7 +9520,7 @@
         <v>59</v>
       </c>
       <c r="C67" t="n">
-        <v>0.539778722851937</v>
+        <v>0.483173627789585</v>
       </c>
       <c r="D67" t="s">
         <v>56</v>
@@ -9529,10 +9529,10 @@
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68">
@@ -9543,7 +9543,7 @@
         <v>59</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0251202368853526</v>
+        <v>0.0350451497141202</v>
       </c>
       <c r="D68" t="s">
         <v>56</v>
@@ -9552,10 +9552,10 @@
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69">
@@ -9566,7 +9566,7 @@
         <v>59</v>
       </c>
       <c r="C69" t="n">
-        <v>0.269889361425969</v>
+        <v>0.276972216967106</v>
       </c>
       <c r="D69" t="s">
         <v>56</v>
@@ -9575,10 +9575,10 @@
         <v>8</v>
       </c>
       <c r="F69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70">
@@ -9589,7 +9589,7 @@
         <v>60</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.290700949866906</v>
+        <v>-0.289682729751161</v>
       </c>
       <c r="D70" t="s">
         <v>56</v>
@@ -9598,10 +9598,10 @@
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71">
@@ -9612,7 +9612,7 @@
         <v>60</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.581401899733811</v>
+        <v>-0.579365459502321</v>
       </c>
       <c r="D71" t="s">
         <v>56</v>
@@ -9621,10 +9621,10 @@
         <v>8</v>
       </c>
       <c r="F71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72">
@@ -9635,7 +9635,7 @@
         <v>60</v>
       </c>
       <c r="C72" t="n">
-        <v>1.30434872663057</v>
+        <v>1.31734466104554</v>
       </c>
       <c r="D72" t="s">
         <v>56</v>
@@ -9644,10 +9644,10 @@
         <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73">
@@ -9658,7 +9658,7 @@
         <v>60</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.61923756742091</v>
+        <v>-1.6102183175902</v>
       </c>
       <c r="D73" t="s">
         <v>56</v>
@@ -9667,10 +9667,10 @@
         <v>8</v>
       </c>
       <c r="F73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74">
@@ -9681,7 +9681,7 @@
         <v>60</v>
       </c>
       <c r="C74" t="n">
-        <v>1.67048522986495</v>
+        <v>1.68570544330937</v>
       </c>
       <c r="D74" t="s">
         <v>56</v>
@@ -9690,10 +9690,10 @@
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75">
@@ -9704,7 +9704,7 @@
         <v>60</v>
       </c>
       <c r="C75" t="n">
-        <v>0.412029867448975</v>
+        <v>0.424272898624803</v>
       </c>
       <c r="D75" t="s">
         <v>56</v>
@@ -9713,10 +9713,10 @@
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76">
@@ -9727,7 +9727,7 @@
         <v>60</v>
       </c>
       <c r="C76" t="n">
-        <v>0.836698285217889</v>
+        <v>0.849207775608447</v>
       </c>
       <c r="D76" t="s">
         <v>56</v>
@@ -9736,10 +9736,10 @@
         <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77">
@@ -9750,7 +9750,7 @@
         <v>60</v>
       </c>
       <c r="C77" t="n">
-        <v>1.01767419793838</v>
+        <v>0.982584361758331</v>
       </c>
       <c r="D77" t="s">
         <v>56</v>
@@ -9759,10 +9759,10 @@
         <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78">
@@ -9773,7 +9773,7 @@
         <v>60</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.713757564977449</v>
+        <v>-0.703526470681449</v>
       </c>
       <c r="D78" t="s">
         <v>56</v>
@@ -9782,10 +9782,10 @@
         <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79">
@@ -9796,7 +9796,7 @@
         <v>60</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.888153269834458</v>
+        <v>-0.918959179613719</v>
       </c>
       <c r="D79" t="s">
         <v>56</v>
@@ -9805,10 +9805,10 @@
         <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G79" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80">
@@ -9819,7 +9819,7 @@
         <v>60</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.23333967768956</v>
+        <v>-1.22901973559805</v>
       </c>
       <c r="D80" t="s">
         <v>56</v>
@@ -9828,10 +9828,10 @@
         <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81">
@@ -9842,7 +9842,7 @@
         <v>60</v>
       </c>
       <c r="C81" t="n">
-        <v>0.531060718045346</v>
+        <v>0.538324753093836</v>
       </c>
       <c r="D81" t="s">
         <v>56</v>
@@ -9851,10 +9851,10 @@
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G81" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -9896,26 +9896,9 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>2.63181998579447</v>
+        <v>2.60278527359852</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.19169084770864</v>
-      </c>
-      <c r="E3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9967,7 +9950,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00207305009925521</v>
+        <v>0.0014539665059619</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -9993,7 +9976,7 @@
         <v>54</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0365677655911336</v>
+        <v>0.030998789656581</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
@@ -10050,7 +10033,7 @@
         <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>0.579185343764877</v>
+        <v>0.583073865024843</v>
       </c>
       <c r="D2" t="s">
         <v>65</v>
@@ -10059,10 +10042,10 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -10073,7 +10056,7 @@
         <v>64</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0919307756463223</v>
+        <v>0.0688184089436672</v>
       </c>
       <c r="D3" t="s">
         <v>65</v>
@@ -10082,21 +10065,21 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.359192558993653</v>
+        <v>-0.358446303504688</v>
       </c>
       <c r="D4" t="s">
         <v>65</v>
@@ -10105,10 +10088,10 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -10119,7 +10102,7 @@
         <v>64</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0196206373157755</v>
+        <v>-0.0191862218629149</v>
       </c>
       <c r="D5" t="s">
         <v>65</v>
@@ -10128,10 +10111,10 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -10142,7 +10125,7 @@
         <v>64</v>
       </c>
       <c r="C6" t="n">
-        <v>0.110097229749673</v>
+        <v>0.11184346066294</v>
       </c>
       <c r="D6" t="s">
         <v>65</v>
@@ -10151,10 +10134,10 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -10165,7 +10148,7 @@
         <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.269883543075431</v>
+        <v>-0.269426437708791</v>
       </c>
       <c r="D7" t="s">
         <v>65</v>
@@ -10174,10 +10157,10 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -10188,7 +10171,7 @@
         <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0291682619065981</v>
+        <v>0.0306399326121652</v>
       </c>
       <c r="D8" t="s">
         <v>65</v>
@@ -10197,10 +10180,10 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -10211,7 +10194,7 @@
         <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.128692632571673</v>
+        <v>-0.127756521890294</v>
       </c>
       <c r="D9" t="s">
         <v>65</v>
@@ -10220,10 +10203,10 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -10234,7 +10217,7 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.139895593969963</v>
+        <v>-0.138997490537291</v>
       </c>
       <c r="D10" t="s">
         <v>65</v>
@@ -10243,10 +10226,10 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -10257,7 +10240,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.228313396951502</v>
+        <v>-0.227715260403345</v>
       </c>
       <c r="D11" t="s">
         <v>65</v>
@@ -10266,10 +10249,10 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -10280,7 +10263,7 @@
         <v>64</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0529927414498165</v>
+        <v>-0.0517998107646346</v>
       </c>
       <c r="D12" t="s">
         <v>65</v>
@@ -10289,10 +10272,10 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -10303,7 +10286,7 @@
         <v>64</v>
       </c>
       <c r="C13" t="n">
-        <v>0.135466452293389</v>
+        <v>0.13037741405601</v>
       </c>
       <c r="D13" t="s">
         <v>65</v>
@@ -10312,10 +10295,10 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -10326,7 +10309,7 @@
         <v>64</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.119817455369672</v>
+        <v>-0.118851234697262</v>
       </c>
       <c r="D14" t="s">
         <v>65</v>
@@ -10335,10 +10318,10 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -10349,7 +10332,7 @@
         <v>64</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0993342275637402</v>
+        <v>0.0908381035984644</v>
       </c>
       <c r="D15" t="s">
         <v>65</v>
@@ -10358,10 +10341,10 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -10372,7 +10355,7 @@
         <v>64</v>
       </c>
       <c r="C16" t="n">
-        <v>0.134604291087691</v>
+        <v>0.13643366483634</v>
       </c>
       <c r="D16" t="s">
         <v>65</v>
@@ -10381,10 +10364,10 @@
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -10395,7 +10378,7 @@
         <v>64</v>
       </c>
       <c r="C17" t="n">
-        <v>1.53767688200556</v>
+        <v>1.54426633007923</v>
       </c>
       <c r="D17" t="s">
         <v>65</v>
@@ -10404,10 +10387,10 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
